--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.26815476787959</v>
+        <v>3.456075149780434</v>
       </c>
       <c r="D2" t="n">
-        <v>23.62502126354203</v>
+        <v>3.83906595532558</v>
       </c>
       <c r="E2" t="n">
-        <v>1.673311332009087</v>
+        <v>0.2719130914514767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4194028781378769</v>
+        <v>0.06815296769740509</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.92153210386142</v>
+        <v>2.912248966877481</v>
       </c>
       <c r="D3" t="n">
-        <v>22.78621550726627</v>
+        <v>3.70276001993077</v>
       </c>
       <c r="E3" t="n">
-        <v>1.673311332009087</v>
+        <v>0.2719130914514767</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4194028781378769</v>
+        <v>0.06815296769740509</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
